--- a/src/test/resources/ImportTemplate/Pushdown - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown - Flat File-SQL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C34AA40-46E2-44FD-A34E-8CBF56D2C289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2521A989-6CA6-4649-829F-9FE32AE2EC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
     <t>|</t>
   </si>
   <si>
-    <t>R001_FlatFile_SQL_Pushdown</t>
+    <t>R00_FlatFile-SQL_Pushdown</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Pushdown - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown - Flat File-SQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2521A989-6CA6-4649-829F-9FE32AE2EC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7EA97E-B8B5-41FA-8C38-C2F5DFA66BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
     <t>|</t>
   </si>
   <si>
-    <t>R00_FlatFile-SQL_Pushdown</t>
+    <t>Pushdown_ImportSQL--File-FlatFile-SQL_Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Pushdown - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown - Flat File-SQL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE7EA97E-B8B5-41FA-8C38-C2F5DFA66BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE0CCE9-2953-4397-8E2D-63AEC271C7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
     <t>|</t>
   </si>
   <si>
-    <t>Pushdown_ImportSQL--File-FlatFile-SQL_Customer</t>
+    <t>Pushdown_ImportSQL__File_FlatFile_SQL_Customer</t>
   </si>
 </sst>
 </file>
